--- a/experiments/20250623/iteration_0/raw_data/raw_absorbance_i0.xlsx
+++ b/experiments/20250623/iteration_0/raw_data/raw_absorbance_i0.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Surfactant\0620\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Surfactant\0623\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC525386-D504-4844-A956-CDE0B6CC3257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{649BC834-ACA2-41B7-8A5B-8698EF9FE6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="9528" windowHeight="10356"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="9528" windowHeight="10356"/>
   </bookViews>
   <sheets>
     <sheet name="Plate 1 - Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MethodPointer1">-1607757088</definedName>
-    <definedName name="MethodPointer2">538</definedName>
+    <definedName name="MethodPointer1">782958464</definedName>
+    <definedName name="MethodPointer2">522</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
     <t>Experiment File Path:</t>
   </si>
   <si>
-    <t>D:\Surfactant\0620\ot-0.xpt</t>
+    <t>D:\Surfactant\0623\ot-0.xpt</t>
   </si>
   <si>
     <t>Protocol File Path:</t>
@@ -97,7 +97,7 @@
     <t>Absorbance Endpoint</t>
   </si>
   <si>
-    <t>C1..C12</t>
+    <t>B1..B12</t>
   </si>
   <si>
     <t>Wavelengths:  600</t>
@@ -172,7 +172,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,43 +193,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF247CBD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF428EC7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5197CC"/>
+        <fgColor rgb="FF7EB2DB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF247CBD"/>
+        <fgColor rgb="FF8DBCE0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF60A0D1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E0F4"/>
+        <fgColor rgb="FF9CC5E5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F3FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DBCE0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -261,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -299,9 +293,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -659,7 +650,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>45828</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -667,7 +658,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>0.4435763888888889</v>
+        <v>0.44186342592592592</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -747,7 +738,7 @@
         <v>24</v>
       </c>
       <c r="B22">
-        <v>24.6</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -813,18 +804,42 @@
       <c r="B26" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
+      <c r="C26" s="9">
+        <v>1.96</v>
+      </c>
+      <c r="D26" s="9">
+        <v>1.915</v>
+      </c>
+      <c r="E26" s="10">
+        <v>1.627</v>
+      </c>
+      <c r="F26" s="11">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G26" s="12">
+        <v>0.88600000000000001</v>
+      </c>
+      <c r="H26" s="13">
+        <v>0.754</v>
+      </c>
+      <c r="I26" s="14">
+        <v>3.9E-2</v>
+      </c>
+      <c r="J26" s="14">
+        <v>3.9E-2</v>
+      </c>
+      <c r="K26" s="13">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="L26" s="13">
+        <v>0.86</v>
+      </c>
+      <c r="M26" s="14">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="N26" s="14">
+        <v>9.6000000000000002E-2</v>
+      </c>
       <c r="O26" s="8">
         <v>600</v>
       </c>
@@ -833,42 +848,18 @@
       <c r="B27" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="9">
-        <v>1.56</v>
-      </c>
-      <c r="D27" s="10">
-        <v>1.474</v>
-      </c>
-      <c r="E27" s="11">
-        <v>1.917</v>
-      </c>
-      <c r="F27" s="12">
-        <v>1.3420000000000001</v>
-      </c>
-      <c r="G27" s="13">
-        <v>0.376</v>
-      </c>
-      <c r="H27" s="13">
-        <v>0.38</v>
-      </c>
-      <c r="I27" s="14">
-        <v>0.04</v>
-      </c>
-      <c r="J27" s="14">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="K27" s="15">
-        <v>0.90400000000000003</v>
-      </c>
-      <c r="L27" s="15">
-        <v>0.86599999999999999</v>
-      </c>
-      <c r="M27" s="14">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="N27" s="14">
-        <v>4.3999999999999997E-2</v>
-      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
       <c r="O27" s="8">
         <v>600</v>
       </c>
